--- a/Battery Charger Project/Excel/BOM/BOM V2 UNIT.xlsx
+++ b/Battery Charger Project/Excel/BOM/BOM V2 UNIT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2476CA4E-FC1A-4A98-B4C5-96CF801338A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC5E4F78-10C8-4999-9D5B-6A34B8E08944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{399A400B-C522-4FE4-B704-6D3A9F06170E}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{399A400B-C522-4FE4-B704-6D3A9F06170E}"/>
   </bookViews>
   <sheets>
     <sheet name="Minimum" sheetId="3" r:id="rId1"/>
@@ -623,12 +623,6 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
@@ -642,6 +636,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -743,6 +743,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -750,15 +759,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -799,13 +799,6 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
       <fill>
         <patternFill patternType="none">
@@ -984,41 +977,48 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1068,24 +1068,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{EEAF1036-AA28-4E30-BD9A-19D4203E5E9C}" name="Table9" displayName="Table9" ref="A1:H19" headerRowDxfId="27" dataDxfId="26" headerRowBorderDxfId="24" tableBorderDxfId="25" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{EEAF1036-AA28-4E30-BD9A-19D4203E5E9C}" name="Table9" displayName="Table9" ref="A1:H19" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="A1:H19" xr:uid="{59A65182-955A-411F-909C-5E992C97166C}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{24419B8B-FF43-4B51-A546-C265CCDC1D88}" name="Item use" totalsRowLabel="Total" dataDxfId="21" totalsRowDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{73565926-C3E1-4407-88D4-758E382675EA}" name="Description" dataDxfId="19" totalsRowDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{33CB0387-9EC9-4F69-99BC-9960DEF33C0D}" name="Product number" dataDxfId="17" totalsRowDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{CDA3F275-2D24-4F2E-AAF7-0E5247C18A95}" name="Vendor" dataDxfId="15" totalsRowDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{4B82A4F9-F428-4DF2-B1D8-CB81C6BF65C0}" name="Link" dataDxfId="13" totalsRowDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{35F514A8-DBF2-480B-8998-E9F53152D339}" name="Min quantity" dataDxfId="11" totalsRowDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{10F70241-F70D-4760-BF6C-25A92BDA41AD}" name="Unit price" dataDxfId="9" totalsRowDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{11A43384-0E2E-44C1-835E-B53743CB0889}" name="Total cost" totalsRowFunction="sum" dataDxfId="7" totalsRowDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{24419B8B-FF43-4B51-A546-C265CCDC1D88}" name="Item use" totalsRowLabel="Total" dataDxfId="22" totalsRowDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{73565926-C3E1-4407-88D4-758E382675EA}" name="Description" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{33CB0387-9EC9-4F69-99BC-9960DEF33C0D}" name="Product number" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{CDA3F275-2D24-4F2E-AAF7-0E5247C18A95}" name="Vendor" dataDxfId="16" totalsRowDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{4B82A4F9-F428-4DF2-B1D8-CB81C6BF65C0}" name="Link" dataDxfId="14" totalsRowDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{35F514A8-DBF2-480B-8998-E9F53152D339}" name="Min quantity" dataDxfId="12" totalsRowDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{10F70241-F70D-4760-BF6C-25A92BDA41AD}" name="Unit price" dataDxfId="10" totalsRowDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{11A43384-0E2E-44C1-835E-B53743CB0889}" name="Total cost" totalsRowFunction="sum" dataDxfId="8" totalsRowDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{44A5CCCD-EF1A-41C4-9A28-211F14A4F8B5}" name="Table10" displayName="Table10" ref="A1:I19" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="4" tableBorderDxfId="5" totalsRowBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{44A5CCCD-EF1A-41C4-9A28-211F14A4F8B5}" name="Table10" displayName="Table10" ref="A1:I19" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4" totalsRowBorderDxfId="3">
   <autoFilter ref="A1:I19" xr:uid="{D59A0370-B28F-4833-BBF6-73CA5F258DAA}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{A671E009-E1D1-415B-AB06-EBE4E463EC9A}" name="item use" dataDxfId="2"/>
@@ -1477,7 +1477,7 @@
       <c r="F2" s="5">
         <v>4</v>
       </c>
-      <c r="G2" s="32">
+      <c r="G2" s="30">
         <v>5.25</v>
       </c>
       <c r="H2" s="7">
@@ -1504,7 +1504,7 @@
       <c r="F3" s="5">
         <v>1</v>
       </c>
-      <c r="G3" s="32">
+      <c r="G3" s="30">
         <v>20.09</v>
       </c>
       <c r="H3" s="7">
@@ -1527,7 +1527,7 @@
       <c r="F4" s="5">
         <v>1</v>
       </c>
-      <c r="G4" s="32"/>
+      <c r="G4" s="30"/>
       <c r="H4" s="7">
         <f>Minimum!$G4*Minimum!$F4</f>
         <v>0</v>
@@ -1552,7 +1552,7 @@
       <c r="F5" s="5">
         <v>1</v>
       </c>
-      <c r="G5" s="32">
+      <c r="G5" s="30">
         <v>0.41</v>
       </c>
       <c r="H5" s="7">
@@ -1579,7 +1579,7 @@
       <c r="F6" s="5">
         <v>1</v>
       </c>
-      <c r="G6" s="32">
+      <c r="G6" s="30">
         <v>2.23</v>
       </c>
       <c r="H6" s="7">
@@ -1606,7 +1606,7 @@
       <c r="F7" s="5">
         <v>1</v>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="30">
         <v>1.29</v>
       </c>
       <c r="H7" s="7">
@@ -1633,7 +1633,7 @@
       <c r="F8" s="5">
         <v>1</v>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="30">
         <v>4.55</v>
       </c>
       <c r="H8" s="7">
@@ -1660,7 +1660,7 @@
       <c r="F9" s="5">
         <v>1</v>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="30">
         <v>0.72</v>
       </c>
       <c r="H9" s="7">
@@ -1687,7 +1687,7 @@
       <c r="F10" s="5">
         <v>4</v>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="30">
         <v>1.94</v>
       </c>
       <c r="H10" s="7">
@@ -1714,7 +1714,7 @@
       <c r="F11" s="5">
         <v>1</v>
       </c>
-      <c r="G11" s="32">
+      <c r="G11" s="30">
         <v>2.44</v>
       </c>
       <c r="H11" s="7">
@@ -1741,7 +1741,7 @@
       <c r="F12" s="5">
         <v>1</v>
       </c>
-      <c r="G12" s="32">
+      <c r="G12" s="30">
         <v>42.9</v>
       </c>
       <c r="H12" s="7">
@@ -1768,7 +1768,7 @@
       <c r="F13" s="5">
         <v>1</v>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="30">
         <v>100.01</v>
       </c>
       <c r="H13" s="7">
@@ -1789,7 +1789,7 @@
       <c r="F14" s="5">
         <v>1</v>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="30">
         <v>70</v>
       </c>
       <c r="H14" s="7">
@@ -1828,7 +1828,7 @@
       <c r="F16">
         <v>1</v>
       </c>
-      <c r="G16" s="33">
+      <c r="G16" s="31">
         <v>40</v>
       </c>
       <c r="H16" s="11">
@@ -1885,32 +1885,32 @@
     </row>
     <row r="20" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
+      <c r="A22" s="32"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="20"/>
+      <c r="B23" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1954,31 +1954,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="I1" s="29" t="s">
+      <c r="I1" s="27" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       <c r="G2" s="6">
         <v>10</v>
       </c>
-      <c r="H2" s="32">
+      <c r="H2" s="30">
         <v>3.61</v>
       </c>
       <c r="I2" s="7">
@@ -2034,7 +2034,7 @@
       <c r="G3" s="6">
         <v>2</v>
       </c>
-      <c r="H3" s="32">
+      <c r="H3" s="30">
         <v>20.09</v>
       </c>
       <c r="I3" s="7">
@@ -2058,7 +2058,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="5"/>
-      <c r="H4" s="32"/>
+      <c r="H4" s="30"/>
       <c r="I4" s="7">
         <f>Suggested!$H4*Suggested!$G4</f>
         <v>0</v>
@@ -2086,7 +2086,7 @@
       <c r="G5" s="6">
         <v>10</v>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="30">
         <v>0.25</v>
       </c>
       <c r="I5" s="7">
@@ -2116,7 +2116,7 @@
       <c r="G6" s="6">
         <v>3</v>
       </c>
-      <c r="H6" s="32">
+      <c r="H6" s="30">
         <v>2.23</v>
       </c>
       <c r="I6" s="7">
@@ -2146,7 +2146,7 @@
       <c r="G7" s="6">
         <v>3</v>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="30">
         <v>1.29</v>
       </c>
       <c r="I7" s="7">
@@ -2176,7 +2176,7 @@
       <c r="G8" s="6">
         <v>2</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="30">
         <v>4.55</v>
       </c>
       <c r="I8" s="7">
@@ -2206,7 +2206,7 @@
       <c r="G9" s="6">
         <v>2</v>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="30">
         <v>0.72</v>
       </c>
       <c r="I9" s="7">
@@ -2236,7 +2236,7 @@
       <c r="G10" s="6">
         <v>5</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="30">
         <v>1.94</v>
       </c>
       <c r="I10" s="7">
@@ -2266,7 +2266,7 @@
       <c r="G11" s="6">
         <v>2</v>
       </c>
-      <c r="H11" s="32">
+      <c r="H11" s="30">
         <v>2.44</v>
       </c>
       <c r="I11" s="7">
@@ -2296,7 +2296,7 @@
       <c r="G12" s="6">
         <v>1</v>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="30">
         <v>42.9</v>
       </c>
       <c r="I12" s="7">
@@ -2326,7 +2326,7 @@
       <c r="G13" s="6">
         <v>1</v>
       </c>
-      <c r="H13" s="32">
+      <c r="H13" s="30">
         <v>100.01</v>
       </c>
       <c r="I13" s="7">
@@ -2350,7 +2350,7 @@
       <c r="G14" s="5">
         <v>1</v>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="30">
         <v>70</v>
       </c>
       <c r="I14" s="7">
@@ -2374,7 +2374,7 @@
       <c r="G15" s="5">
         <v>1</v>
       </c>
-      <c r="H15" s="32">
+      <c r="H15" s="30">
         <v>5</v>
       </c>
       <c r="I15" s="7">
@@ -2406,7 +2406,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="26" t="s">
         <v>64</v>
       </c>
       <c r="B17" s="13" t="s">
@@ -2418,39 +2418,39 @@
       <c r="F17" s="12"/>
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
-      <c r="I17" s="27" cm="1">
+      <c r="I17" s="25" cm="1">
         <f t="array" ref="I17">SUM(I2:I16*0.2)</f>
         <v>74.474000000000004</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="25"/>
+      <c r="B18" s="23"/>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
       <c r="H18" s="15"/>
-      <c r="I18" s="24">
+      <c r="I18" s="22">
         <f>SUM($I$2:$I$17)</f>
         <v>446.84399999999999</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="21">
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="19">
         <f>SUM(I2:I13,I15:I16)+(0.2*SUM(I15:I16,I2:I13))</f>
         <v>362.84399999999999</v>
       </c>

--- a/Battery Charger Project/Excel/BOM/BOM V2 UNIT.xlsx
+++ b/Battery Charger Project/Excel/BOM/BOM V2 UNIT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC5E4F78-10C8-4999-9D5B-6A34B8E08944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832AC17C-6418-4DD0-AE92-E1B66B961976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{399A400B-C522-4FE4-B704-6D3A9F06170E}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8928" xr2:uid="{399A400B-C522-4FE4-B704-6D3A9F06170E}"/>
   </bookViews>
   <sheets>
     <sheet name="Minimum" sheetId="3" r:id="rId1"/>

--- a/Battery Charger Project/Excel/BOM/BOM V2 UNIT.xlsx
+++ b/Battery Charger Project/Excel/BOM/BOM V2 UNIT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832AC17C-6418-4DD0-AE92-E1B66B961976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586F8AF0-FF7B-4029-AD82-078A7065455B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8928" xr2:uid="{399A400B-C522-4FE4-B704-6D3A9F06170E}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{399A400B-C522-4FE4-B704-6D3A9F06170E}"/>
   </bookViews>
   <sheets>
     <sheet name="Minimum" sheetId="3" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="80">
   <si>
     <t>Item use</t>
   </si>
@@ -296,6 +296,12 @@
   </si>
   <si>
     <t>item use</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/en/ProductDetail/Phoenix-Contact/1935174?qs=QWULklcAmSR8B7o4YouITA%3D%3D</t>
+  </si>
+  <si>
+    <t>IRF200B211-ND</t>
   </si>
 </sst>
 </file>
@@ -1568,7 +1574,7 @@
         <v>26</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>11</v>
@@ -1652,10 +1658,10 @@
         <v>39</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="F9" s="5">
         <v>1</v>

--- a/Battery Charger Project/Excel/BOM/BOM V2 UNIT.xlsx
+++ b/Battery Charger Project/Excel/BOM/BOM V2 UNIT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586F8AF0-FF7B-4029-AD82-078A7065455B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{849EE4DA-32F7-44CC-8409-F5325EB8FCD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{399A400B-C522-4FE4-B704-6D3A9F06170E}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{399A400B-C522-4FE4-B704-6D3A9F06170E}"/>
   </bookViews>
   <sheets>
     <sheet name="Minimum" sheetId="3" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="112">
   <si>
     <t>Item use</t>
   </si>
@@ -302,6 +302,102 @@
   </si>
   <si>
     <t>IRF200B211-ND</t>
+  </si>
+  <si>
+    <t>HV divider resistor</t>
+  </si>
+  <si>
+    <t>RES 5.1K OHM 1% 3/4W 2010</t>
+  </si>
+  <si>
+    <t>RC2010FK-075K1L</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/RC2010FK-075K1L/5921466</t>
+  </si>
+  <si>
+    <t>RC2010FK-13820RL</t>
+  </si>
+  <si>
+    <t>RES 820 OHM 1% 3/4W 2010</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/RC2010FK-13820RL/17016426</t>
+  </si>
+  <si>
+    <t>RES 3502 300K 1%</t>
+  </si>
+  <si>
+    <t>3502300KFT</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/te-connectivity-passive-product/3502300KFT/9926680</t>
+  </si>
+  <si>
+    <t>Vo divider resistor</t>
+  </si>
+  <si>
+    <t>RES 5.6K OHM 1% 1.25W 2010</t>
+  </si>
+  <si>
+    <t>CRGP2010F5K6</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/te-connectivity-passive-product/CRGP2010F5K6/8577271</t>
+  </si>
+  <si>
+    <t>RES SMD 620 OHM 1% 1W 2010</t>
+  </si>
+  <si>
+    <t>CRCW2010620RFKEFHP</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/vishay-dale/CRCW2010620RFKEFHP/2222172</t>
+  </si>
+  <si>
+    <t>RES 51K OHM 1% 3/4W 2010</t>
+  </si>
+  <si>
+    <t>RC2010FK-0751KL</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/RC2010FK-0751KL/5921434</t>
+  </si>
+  <si>
+    <t>CAP CER 0.1UF 50V X7R 0805</t>
+  </si>
+  <si>
+    <t>CC0805KRX7R9BB104</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/CC0805KRX7R9BB104/302874</t>
+  </si>
+  <si>
+    <t>Decap 0.1UF</t>
+  </si>
+  <si>
+    <t>Decap 1UF</t>
+  </si>
+  <si>
+    <t>CAP CER 1UF 50V X7R 0805</t>
+  </si>
+  <si>
+    <t>CC0805JKX7R9BB105</t>
+  </si>
+  <si>
+    <t>CC0805JKX7R9BB105 YAGEO | Ceramic Capacitors | DigiKey</t>
+  </si>
+  <si>
+    <t>Decap 10UF</t>
+  </si>
+  <si>
+    <t>CAP CER 10UF 16V X5R 0805</t>
+  </si>
+  <si>
+    <t>CC0805KRX5R7BB106</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/CC0805KRX5R7BB106/7164386</t>
   </si>
 </sst>
 </file>
@@ -609,7 +705,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -642,12 +738,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1074,8 +1182,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{EEAF1036-AA28-4E30-BD9A-19D4203E5E9C}" name="Table9" displayName="Table9" ref="A1:H19" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
-  <autoFilter ref="A1:H19" xr:uid="{59A65182-955A-411F-909C-5E992C97166C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{EEAF1036-AA28-4E30-BD9A-19D4203E5E9C}" name="Table9" displayName="Table9" ref="A1:H28" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+  <autoFilter ref="A1:H28" xr:uid="{59A65182-955A-411F-909C-5E992C97166C}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{24419B8B-FF43-4B51-A546-C265CCDC1D88}" name="Item use" totalsRowLabel="Total" dataDxfId="22" totalsRowDxfId="21"/>
     <tableColumn id="2" xr3:uid="{73565926-C3E1-4407-88D4-758E382675EA}" name="Description" dataDxfId="20" totalsRowDxfId="19"/>
@@ -1425,20 +1533,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{554B8B7F-D3DD-4982-98A6-18382FC88934}">
-  <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="62.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="92.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="62.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="92.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1464,464 +1572,706 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="23">
         <v>4</v>
       </c>
-      <c r="G2" s="30">
+      <c r="G2" s="34">
         <v>5.25</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="35">
         <f>Minimum!$G2*Minimum!$F2</f>
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="5">
-        <v>1</v>
-      </c>
-      <c r="G3" s="30">
+      <c r="F3" s="23">
+        <v>1</v>
+      </c>
+      <c r="G3" s="34">
         <v>20.09</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="35">
         <f>Minimum!$G3*Minimum!$F3</f>
         <v>20.09</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5">
-        <v>1</v>
-      </c>
-      <c r="G4" s="30"/>
-      <c r="H4" s="7">
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23">
+        <v>1</v>
+      </c>
+      <c r="G4" s="34"/>
+      <c r="H4" s="35">
         <f>Minimum!$G4*Minimum!$F4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="5">
-        <v>1</v>
-      </c>
-      <c r="G5" s="30">
+      <c r="F5" s="23">
+        <v>1</v>
+      </c>
+      <c r="G5" s="34">
         <v>0.41</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="35">
         <f>Minimum!$G5*Minimum!$F5</f>
         <v>0.41</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="5">
-        <v>1</v>
-      </c>
-      <c r="G6" s="30">
+      <c r="F6" s="23">
+        <v>1</v>
+      </c>
+      <c r="G6" s="34">
         <v>2.23</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="35">
         <f>Minimum!$G6*Minimum!$F6</f>
         <v>2.23</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="5">
-        <v>1</v>
-      </c>
-      <c r="G7" s="30">
+      <c r="F7" s="23">
+        <v>1</v>
+      </c>
+      <c r="G7" s="34">
         <v>1.29</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="35">
         <f>Minimum!$G7*Minimum!$F7</f>
         <v>1.29</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="5">
-        <v>1</v>
-      </c>
-      <c r="G8" s="30">
+      <c r="F8" s="23">
+        <v>1</v>
+      </c>
+      <c r="G8" s="34">
         <v>4.55</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="35">
         <f>Minimum!$G8*Minimum!$F8</f>
         <v>4.55</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="F9" s="5">
-        <v>1</v>
-      </c>
-      <c r="G9" s="30">
+      <c r="F9" s="23">
+        <v>1</v>
+      </c>
+      <c r="G9" s="34">
         <v>0.72</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="35">
         <f>Minimum!$G9*Minimum!$F9</f>
         <v>0.72</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="23">
         <v>4</v>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="34">
         <v>1.94</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="35">
         <f>Minimum!$G10*Minimum!$F10</f>
         <v>7.76</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="5">
-        <v>1</v>
-      </c>
-      <c r="G11" s="30">
+      <c r="F11" s="23">
+        <v>1</v>
+      </c>
+      <c r="G11" s="34">
         <v>2.44</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="35">
         <f>Minimum!$G11*Minimum!$F11</f>
         <v>2.44</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="F12" s="23">
+        <v>1</v>
+      </c>
+      <c r="G12" s="34">
+        <v>0.23</v>
+      </c>
+      <c r="H12" s="35">
+        <f>Minimum!$G12*Minimum!$F12</f>
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="23">
+        <v>1</v>
+      </c>
+      <c r="G13" s="34">
+        <v>0.23</v>
+      </c>
+      <c r="H13" s="35">
+        <f>Minimum!$G13*Minimum!$F13</f>
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="F14" s="23">
+        <v>1</v>
+      </c>
+      <c r="G14" s="34">
+        <v>0.95</v>
+      </c>
+      <c r="H14" s="35">
+        <f>Minimum!$G14*Minimum!$F14</f>
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="23">
+        <v>1</v>
+      </c>
+      <c r="G15" s="34">
+        <v>0.45</v>
+      </c>
+      <c r="H15" s="35">
+        <f>Minimum!$G15*Minimum!$F15</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" s="23">
+        <v>1</v>
+      </c>
+      <c r="G16" s="34">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H16" s="35">
+        <f>Minimum!$G16*Minimum!$F16</f>
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" s="23">
+        <v>1</v>
+      </c>
+      <c r="G17" s="34">
+        <v>0.23</v>
+      </c>
+      <c r="H17" s="35">
+        <f>Minimum!$G17*Minimum!$F17</f>
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" s="41">
+        <v>1</v>
+      </c>
+      <c r="G18" s="43">
+        <v>0.18</v>
+      </c>
+      <c r="H18" s="35">
+        <f>Minimum!$G18*Minimum!$F18</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="F19" s="41">
+        <v>1</v>
+      </c>
+      <c r="G19" s="43">
+        <v>0.38</v>
+      </c>
+      <c r="H19" s="35">
+        <f>Minimum!$G19*Minimum!$F19</f>
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="F20" s="41">
+        <v>1</v>
+      </c>
+      <c r="G20" s="43">
+        <v>0.63</v>
+      </c>
+      <c r="H20" s="35">
+        <f>Minimum!$G20*Minimum!$F20</f>
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B21" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C21" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E21" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="5">
-        <v>1</v>
-      </c>
-      <c r="G12" s="30">
+      <c r="F21" s="5">
+        <v>1</v>
+      </c>
+      <c r="G21" s="30">
         <v>42.9</v>
       </c>
-      <c r="H12" s="7">
-        <f>Minimum!$G12*Minimum!$F12</f>
+      <c r="H21" s="7">
+        <f>Minimum!$G21*Minimum!$F21</f>
         <v>42.9</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B22" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C22" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D22" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E22" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="5">
-        <v>1</v>
-      </c>
-      <c r="G13" s="30">
+      <c r="F22" s="23">
+        <v>1</v>
+      </c>
+      <c r="G22" s="34">
         <v>100.01</v>
       </c>
-      <c r="H13" s="7">
-        <f>Minimum!$G13*Minimum!$F13</f>
+      <c r="H22" s="35">
+        <f>Minimum!$G22*Minimum!$F22</f>
         <v>100.01</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B23" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5">
-        <v>1</v>
-      </c>
-      <c r="G14" s="30">
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5">
+        <v>1</v>
+      </c>
+      <c r="G23" s="30">
         <v>70</v>
       </c>
-      <c r="H14" s="7">
-        <f>Minimum!$G14*Minimum!$F14</f>
+      <c r="H23" s="7">
+        <f>Minimum!$G23*Minimum!$F23</f>
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B24" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10">
-        <v>1</v>
-      </c>
-      <c r="G15" s="18">
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10">
+        <v>1</v>
+      </c>
+      <c r="G24" s="18">
         <v>5</v>
       </c>
-      <c r="H15" s="11">
-        <f>Minimum!$G15*Minimum!$F15</f>
+      <c r="H24" s="11">
+        <f>Minimum!$G24*Minimum!$F24</f>
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+    <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>62</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B25" t="s">
         <v>63</v>
       </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16" s="31">
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" s="31">
         <v>40</v>
       </c>
-      <c r="H16" s="11">
-        <f>Minimum!$G16*Minimum!$F16</f>
+      <c r="H25" s="11">
+        <f>Minimum!$G25*Minimum!$F25</f>
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B26" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="14" cm="1">
-        <f t="array" ref="H17">SUM(H2:H16*0.2)</f>
-        <v>63.680000000000007</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="14" cm="1">
+        <f t="array" ref="H26">SUM(H2:H25*0.2)</f>
+        <v>64.448000000000008</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="16">
-        <f>SUM($H$2:$H$17)</f>
-        <v>382.08</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="17" t="s">
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="16">
+        <f>SUM($H$2:$H$26)</f>
+        <v>386.68799999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="18">
-        <f>SUM(H2:H13,H15:H16)+(0.2*SUM(H15:H16,H2:H13))</f>
-        <v>298.08</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="32" t="s">
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="18">
+        <f>SUM(H2:H22,H24:H25)+(0.2*SUM(H24:H25,H2:H22))</f>
+        <v>302.68799999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="32"/>
-      <c r="B22" s="32"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="33" t="s">
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="38"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="38"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="33"/>
+      <c r="B32" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A21:H22"/>
-    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A30:H31"/>
+    <mergeCell ref="A32:B32"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{32046390-9D20-4E95-936E-007B1D9C044F}"/>
@@ -1933,13 +2283,22 @@
     <hyperlink ref="E9" r:id="rId7" xr:uid="{58DF0253-EC2E-4881-9878-9B007F638B30}"/>
     <hyperlink ref="E10" r:id="rId8" xr:uid="{EEF32F00-A16D-4CCC-A3BA-767973F49E38}"/>
     <hyperlink ref="E11" r:id="rId9" xr:uid="{8D15455B-AA7A-47C6-9E90-212B41F4A8A0}"/>
-    <hyperlink ref="E12" r:id="rId10" location="order-start-development" xr:uid="{B3A6C5F1-4DED-4D01-A760-60C875334C73}"/>
-    <hyperlink ref="E13" r:id="rId11" xr:uid="{EDD8EE77-0F22-435D-8F9B-0EB0F5B6557B}"/>
+    <hyperlink ref="E21" r:id="rId10" location="order-start-development" xr:uid="{B3A6C5F1-4DED-4D01-A760-60C875334C73}"/>
+    <hyperlink ref="E22" r:id="rId11" xr:uid="{EDD8EE77-0F22-435D-8F9B-0EB0F5B6557B}"/>
+    <hyperlink ref="E12" r:id="rId12" xr:uid="{6BFA9585-109F-49A2-8A46-EA4DE3E05DF0}"/>
+    <hyperlink ref="E13" r:id="rId13" xr:uid="{146FA4C1-48D4-42BD-B9E2-312C67A5B0AF}"/>
+    <hyperlink ref="E14" r:id="rId14" xr:uid="{A7F06E00-E6C4-4B52-8E4C-08C83A224993}"/>
+    <hyperlink ref="E15" r:id="rId15" xr:uid="{79ECD72F-0619-4431-A58C-2F358EA5F7A0}"/>
+    <hyperlink ref="E16" r:id="rId16" xr:uid="{868C91EB-5760-4656-A4BD-BBEFFE6CEA00}"/>
+    <hyperlink ref="E17" r:id="rId17" xr:uid="{BB979C8E-EB87-481D-B9D9-03D8AF671AEA}"/>
+    <hyperlink ref="E18" r:id="rId18" xr:uid="{5FD5798E-7964-4D6E-8AD0-782DED9D9B27}"/>
+    <hyperlink ref="E19" r:id="rId19" display="https://www.digikey.com/en/products/detail/yageo/CC0805JKX7R9BB105/7164382" xr:uid="{E84CDA52-DBB3-45C2-A2CD-8D34D2AD3F0E}"/>
+    <hyperlink ref="E20" r:id="rId20" xr:uid="{A4DEB91C-730B-42A5-A016-D61E87732207}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId12"/>
+  <pageSetup orientation="portrait" r:id="rId21"/>
   <tableParts count="1">
-    <tablePart r:id="rId13"/>
+    <tablePart r:id="rId22"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1947,19 +2306,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2553C132-7A10-4C14-8263-4317770C79E9}">
   <dimension ref="A1:I19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="66.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="106.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="106.7109375" customWidth="1"/>
+    <col min="6" max="6" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
         <v>77</v>
       </c>
@@ -1988,7 +2347,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -2018,7 +2377,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
@@ -2048,7 +2407,7 @@
         <v>40.18</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>18</v>
       </c>
@@ -2070,7 +2429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>21</v>
       </c>
@@ -2100,7 +2459,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>25</v>
       </c>
@@ -2130,7 +2489,7 @@
         <v>6.6899999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>29</v>
       </c>
@@ -2160,7 +2519,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>33</v>
       </c>
@@ -2190,7 +2549,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>37</v>
       </c>
@@ -2220,7 +2579,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>41</v>
       </c>
@@ -2250,7 +2609,7 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>45</v>
       </c>
@@ -2280,7 +2639,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>49</v>
       </c>
@@ -2310,7 +2669,7 @@
         <v>42.9</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>54</v>
       </c>
@@ -2340,7 +2699,7 @@
         <v>100.01</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>58</v>
       </c>
@@ -2364,7 +2723,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>60</v>
       </c>
@@ -2388,7 +2747,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>62</v>
       </c>
@@ -2411,7 +2770,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
         <v>64</v>
       </c>
@@ -2429,7 +2788,7 @@
         <v>74.474000000000004</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
         <v>66</v>
       </c>
@@ -2445,7 +2804,7 @@
         <v>446.84399999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="21" t="s">
         <v>67</v>
       </c>

--- a/Battery Charger Project/Excel/BOM/BOM V2 UNIT.xlsx
+++ b/Battery Charger Project/Excel/BOM/BOM V2 UNIT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{849EE4DA-32F7-44CC-8409-F5325EB8FCD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA63BF25-9A7A-44C6-846E-C193427B1E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{399A400B-C522-4FE4-B704-6D3A9F06170E}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{399A400B-C522-4FE4-B704-6D3A9F06170E}"/>
   </bookViews>
   <sheets>
     <sheet name="Minimum" sheetId="3" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="116">
   <si>
     <t>Item use</t>
   </si>
@@ -398,6 +398,18 @@
   </si>
   <si>
     <t>https://www.digikey.com/en/products/detail/yageo/CC0805KRX5R7BB106/7164386</t>
+  </si>
+  <si>
+    <t>MCU header pins</t>
+  </si>
+  <si>
+    <t>CONN HEADER VERT 20POS 2.54MM</t>
+  </si>
+  <si>
+    <t>TSW-110-07-F-D</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/samtec-inc/TSW-110-07-F-D/2685964</t>
   </si>
 </sst>
 </file>
@@ -705,7 +717,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -720,10 +732,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
@@ -737,25 +746,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -932,6 +940,7 @@
     <dxf>
       <fill>
         <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -955,6 +964,7 @@
     <dxf>
       <fill>
         <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -978,6 +988,7 @@
     <dxf>
       <fill>
         <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -1001,6 +1012,7 @@
     <dxf>
       <fill>
         <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -1024,6 +1036,7 @@
     <dxf>
       <fill>
         <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -1047,6 +1060,7 @@
     <dxf>
       <fill>
         <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -1070,6 +1084,7 @@
     <dxf>
       <fill>
         <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -1093,6 +1108,7 @@
     <dxf>
       <fill>
         <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -1123,6 +1139,7 @@
     <dxf>
       <fill>
         <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -1534,19 +1551,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{554B8B7F-D3DD-4982-98A6-18382FC88934}">
   <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="62.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="92.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" customWidth="1"/>
+    <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="62.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="92.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1572,610 +1589,616 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+    <row r="2" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="23">
+      <c r="F2" s="20">
         <v>4</v>
       </c>
-      <c r="G2" s="34">
+      <c r="G2" s="30">
         <v>5.25</v>
       </c>
-      <c r="H2" s="35">
+      <c r="H2" s="31">
         <f>Minimum!$G2*Minimum!$F2</f>
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+    <row r="3" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="23">
-        <v>1</v>
-      </c>
-      <c r="G3" s="34">
+      <c r="F3" s="20">
+        <v>1</v>
+      </c>
+      <c r="G3" s="30">
         <v>20.09</v>
       </c>
-      <c r="H3" s="35">
+      <c r="H3" s="31">
         <f>Minimum!$G3*Minimum!$F3</f>
         <v>20.09</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
+    <row r="4" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23">
-        <v>1</v>
-      </c>
-      <c r="G4" s="34"/>
-      <c r="H4" s="35">
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20">
+        <v>1</v>
+      </c>
+      <c r="G4" s="30"/>
+      <c r="H4" s="31">
         <f>Minimum!$G4*Minimum!$F4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
+    <row r="5" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="23">
-        <v>1</v>
-      </c>
-      <c r="G5" s="34">
+      <c r="F5" s="20">
+        <v>1</v>
+      </c>
+      <c r="G5" s="30">
         <v>0.41</v>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="31">
         <f>Minimum!$G5*Minimum!$F5</f>
         <v>0.41</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
+    <row r="6" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="23">
-        <v>1</v>
-      </c>
-      <c r="G6" s="34">
+      <c r="F6" s="20">
+        <v>1</v>
+      </c>
+      <c r="G6" s="30">
         <v>2.23</v>
       </c>
-      <c r="H6" s="35">
+      <c r="H6" s="31">
         <f>Minimum!$G6*Minimum!$F6</f>
         <v>2.23</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
+    <row r="7" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="23">
-        <v>1</v>
-      </c>
-      <c r="G7" s="34">
+      <c r="F7" s="20">
+        <v>1</v>
+      </c>
+      <c r="G7" s="30">
         <v>1.29</v>
       </c>
-      <c r="H7" s="35">
+      <c r="H7" s="31">
         <f>Minimum!$G7*Minimum!$F7</f>
         <v>1.29</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
+    <row r="8" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="33" t="s">
+      <c r="E8" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="23">
-        <v>1</v>
-      </c>
-      <c r="G8" s="34">
+      <c r="F8" s="20">
+        <v>1</v>
+      </c>
+      <c r="G8" s="30">
         <v>4.55</v>
       </c>
-      <c r="H8" s="35">
+      <c r="H8" s="31">
         <f>Minimum!$G8*Minimum!$F8</f>
         <v>4.55</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="32" t="s">
+    <row r="9" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="F9" s="23">
-        <v>1</v>
-      </c>
-      <c r="G9" s="34">
+      <c r="F9" s="20">
+        <v>1</v>
+      </c>
+      <c r="G9" s="30">
         <v>0.72</v>
       </c>
-      <c r="H9" s="35">
+      <c r="H9" s="31">
         <f>Minimum!$G9*Minimum!$F9</f>
         <v>0.72</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+    <row r="10" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="33" t="s">
+      <c r="E10" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="20">
         <v>4</v>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="30">
         <v>1.94</v>
       </c>
-      <c r="H10" s="35">
+      <c r="H10" s="31">
         <f>Minimum!$G10*Minimum!$F10</f>
         <v>7.76</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
+    <row r="11" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="33" t="s">
+      <c r="E11" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="23">
-        <v>1</v>
-      </c>
-      <c r="G11" s="34">
+      <c r="F11" s="20">
+        <v>1</v>
+      </c>
+      <c r="G11" s="30">
         <v>2.44</v>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="31">
         <f>Minimum!$G11*Minimum!$F11</f>
         <v>2.44</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="32" t="s">
+    <row r="12" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="33" t="s">
+      <c r="E12" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="F12" s="23">
-        <v>1</v>
-      </c>
-      <c r="G12" s="34">
+      <c r="F12" s="20">
+        <v>1</v>
+      </c>
+      <c r="G12" s="30">
         <v>0.23</v>
       </c>
-      <c r="H12" s="35">
+      <c r="H12" s="31">
         <f>Minimum!$G12*Minimum!$F12</f>
         <v>0.23</v>
       </c>
     </row>
-    <row r="13" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32" t="s">
+    <row r="13" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="33" t="s">
+      <c r="E13" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="F13" s="23">
-        <v>1</v>
-      </c>
-      <c r="G13" s="34">
+      <c r="F13" s="20">
+        <v>1</v>
+      </c>
+      <c r="G13" s="30">
         <v>0.23</v>
       </c>
-      <c r="H13" s="35">
+      <c r="H13" s="31">
         <f>Minimum!$G13*Minimum!$F13</f>
         <v>0.23</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="32" t="s">
+    <row r="14" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="33" t="s">
+      <c r="E14" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="F14" s="23">
-        <v>1</v>
-      </c>
-      <c r="G14" s="34">
+      <c r="F14" s="20">
+        <v>1</v>
+      </c>
+      <c r="G14" s="30">
         <v>0.95</v>
       </c>
-      <c r="H14" s="35">
+      <c r="H14" s="31">
         <f>Minimum!$G14*Minimum!$F14</f>
         <v>0.95</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="32" t="s">
+    <row r="15" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="33" t="s">
+      <c r="E15" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="F15" s="23">
-        <v>1</v>
-      </c>
-      <c r="G15" s="34">
+      <c r="F15" s="20">
+        <v>1</v>
+      </c>
+      <c r="G15" s="30">
         <v>0.45</v>
       </c>
-      <c r="H15" s="35">
+      <c r="H15" s="31">
         <f>Minimum!$G15*Minimum!$F15</f>
         <v>0.45</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="32" t="s">
+    <row r="16" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="23" t="s">
+      <c r="D16" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="33" t="s">
+      <c r="E16" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="F16" s="23">
-        <v>1</v>
-      </c>
-      <c r="G16" s="34">
+      <c r="F16" s="20">
+        <v>1</v>
+      </c>
+      <c r="G16" s="30">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H16" s="35">
+      <c r="H16" s="31">
         <f>Minimum!$G16*Minimum!$F16</f>
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="17" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="32" t="s">
+    <row r="17" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="C17" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="D17" s="23" t="s">
+      <c r="D17" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="33" t="s">
+      <c r="E17" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="F17" s="23">
-        <v>1</v>
-      </c>
-      <c r="G17" s="34">
+      <c r="F17" s="20">
+        <v>1</v>
+      </c>
+      <c r="G17" s="30">
         <v>0.23</v>
       </c>
-      <c r="H17" s="35">
+      <c r="H17" s="31">
         <f>Minimum!$G17*Minimum!$F17</f>
         <v>0.23</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="40" t="s">
+    <row r="18" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="42" t="s">
+      <c r="C18" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="D18" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="F18" s="41">
-        <v>1</v>
-      </c>
-      <c r="G18" s="43">
+      <c r="F18" s="20">
+        <v>1</v>
+      </c>
+      <c r="G18" s="30">
         <v>0.18</v>
       </c>
-      <c r="H18" s="35">
+      <c r="H18" s="31">
         <f>Minimum!$G18*Minimum!$F18</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="19" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="40" t="s">
+    <row r="19" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C19" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="D19" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="44" t="s">
+      <c r="E19" s="39" t="s">
         <v>107</v>
       </c>
-      <c r="F19" s="41">
-        <v>1</v>
-      </c>
-      <c r="G19" s="43">
+      <c r="F19" s="20">
+        <v>1</v>
+      </c>
+      <c r="G19" s="30">
         <v>0.38</v>
       </c>
-      <c r="H19" s="35">
+      <c r="H19" s="31">
         <f>Minimum!$G19*Minimum!$F19</f>
         <v>0.38</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="40" t="s">
+    <row r="20" spans="1:8" s="32" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="42" t="s">
+      <c r="C20" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="45" t="s">
+      <c r="E20" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="F20" s="41">
-        <v>1</v>
-      </c>
-      <c r="G20" s="43">
+      <c r="F20" s="20">
+        <v>1</v>
+      </c>
+      <c r="G20" s="30">
         <v>0.63</v>
       </c>
-      <c r="H20" s="35">
+      <c r="H20" s="31">
         <f>Minimum!$G20*Minimum!$F20</f>
         <v>0.63</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+    <row r="21" spans="1:8" s="32" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="F21" s="20">
+        <v>4</v>
+      </c>
+      <c r="G21" s="30">
+        <v>1.06</v>
+      </c>
+      <c r="H21" s="31">
+        <f>Minimum!$G21*Minimum!$F21</f>
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B22" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C22" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D22" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E22" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="F21" s="5">
-        <v>1</v>
-      </c>
-      <c r="G21" s="30">
+      <c r="F22" s="20">
+        <v>1</v>
+      </c>
+      <c r="G22" s="30">
         <v>42.9</v>
       </c>
-      <c r="H21" s="7">
-        <f>Minimum!$G21*Minimum!$F21</f>
+      <c r="H22" s="31">
+        <f>Minimum!$G22*Minimum!$F22</f>
         <v>42.9</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="32" t="s">
+    <row r="23" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="23" t="s">
+      <c r="B23" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="37" t="s">
+      <c r="C23" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="D23" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="33" t="s">
+      <c r="E23" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="F22" s="23">
-        <v>1</v>
-      </c>
-      <c r="G22" s="34">
+      <c r="F23" s="20">
+        <v>1</v>
+      </c>
+      <c r="G23" s="30">
         <v>100.01</v>
       </c>
-      <c r="H22" s="35">
-        <f>Minimum!$G22*Minimum!$F22</f>
+      <c r="H23" s="31">
+        <f>Minimum!$G23*Minimum!$F23</f>
         <v>100.01</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B24" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5">
-        <v>1</v>
-      </c>
-      <c r="G23" s="30">
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5">
+        <v>1</v>
+      </c>
+      <c r="G24" s="27">
         <v>70</v>
       </c>
-      <c r="H23" s="7">
-        <f>Minimum!$G23*Minimum!$F23</f>
+      <c r="H24" s="7">
+        <f>Minimum!$G24*Minimum!$F24</f>
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10">
-        <v>1</v>
-      </c>
-      <c r="G24" s="18">
-        <v>5</v>
-      </c>
-      <c r="H24" s="11">
-        <f>Minimum!$G24*Minimum!$F24</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -2185,7 +2208,7 @@
       <c r="F25">
         <v>1</v>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="34">
         <v>40</v>
       </c>
       <c r="H25" s="11">
@@ -2193,7 +2216,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>64</v>
       </c>
@@ -2205,28 +2228,28 @@
       <c r="E26" s="12"/>
       <c r="F26" s="12"/>
       <c r="G26" s="12"/>
-      <c r="H26" s="14" cm="1">
+      <c r="H26" s="35" cm="1">
         <f t="array" ref="H26">SUM(H2:H25*0.2)</f>
-        <v>64.448000000000008</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
+        <v>64.295999999999992</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="16">
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="37">
         <f>SUM($H$2:$H$26)</f>
-        <v>386.68799999999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+        <v>385.77599999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="38" t="s">
         <v>67</v>
       </c>
       <c r="B28" s="10"/>
@@ -2235,38 +2258,38 @@
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
-      <c r="H28" s="18">
-        <f>SUM(H2:H22,H24:H25)+(0.2*SUM(H24:H25,H2:H22))</f>
-        <v>302.68799999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="38" t="s">
+      <c r="H28" s="15">
+        <f>SUM(H2:H23,H25:H25)+(0.2*SUM(H25:H25,H2:H23))</f>
+        <v>301.77599999999995</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="38"/>
-      <c r="C30" s="38"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="38"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="38"/>
-      <c r="D31" s="38"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="38"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="39" t="s">
+      <c r="B30" s="40"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="40"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="40"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="B32" s="39"/>
+      <c r="B32" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2283,8 +2306,8 @@
     <hyperlink ref="E9" r:id="rId7" xr:uid="{58DF0253-EC2E-4881-9878-9B007F638B30}"/>
     <hyperlink ref="E10" r:id="rId8" xr:uid="{EEF32F00-A16D-4CCC-A3BA-767973F49E38}"/>
     <hyperlink ref="E11" r:id="rId9" xr:uid="{8D15455B-AA7A-47C6-9E90-212B41F4A8A0}"/>
-    <hyperlink ref="E21" r:id="rId10" location="order-start-development" xr:uid="{B3A6C5F1-4DED-4D01-A760-60C875334C73}"/>
-    <hyperlink ref="E22" r:id="rId11" xr:uid="{EDD8EE77-0F22-435D-8F9B-0EB0F5B6557B}"/>
+    <hyperlink ref="E22" r:id="rId10" location="order-start-development" xr:uid="{B3A6C5F1-4DED-4D01-A760-60C875334C73}"/>
+    <hyperlink ref="E23" r:id="rId11" xr:uid="{EDD8EE77-0F22-435D-8F9B-0EB0F5B6557B}"/>
     <hyperlink ref="E12" r:id="rId12" xr:uid="{6BFA9585-109F-49A2-8A46-EA4DE3E05DF0}"/>
     <hyperlink ref="E13" r:id="rId13" xr:uid="{146FA4C1-48D4-42BD-B9E2-312C67A5B0AF}"/>
     <hyperlink ref="E14" r:id="rId14" xr:uid="{A7F06E00-E6C4-4B52-8E4C-08C83A224993}"/>
@@ -2294,11 +2317,12 @@
     <hyperlink ref="E18" r:id="rId18" xr:uid="{5FD5798E-7964-4D6E-8AD0-782DED9D9B27}"/>
     <hyperlink ref="E19" r:id="rId19" display="https://www.digikey.com/en/products/detail/yageo/CC0805JKX7R9BB105/7164382" xr:uid="{E84CDA52-DBB3-45C2-A2CD-8D34D2AD3F0E}"/>
     <hyperlink ref="E20" r:id="rId20" xr:uid="{A4DEB91C-730B-42A5-A016-D61E87732207}"/>
+    <hyperlink ref="E21" r:id="rId21" xr:uid="{E128451E-D17C-4706-B25F-D8E54E9529CB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId21"/>
+  <pageSetup orientation="portrait" r:id="rId22"/>
   <tableParts count="1">
-    <tablePart r:id="rId22"/>
+    <tablePart r:id="rId23"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2306,48 +2330,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2553C132-7A10-4C14-8263-4317770C79E9}">
   <dimension ref="A1:I19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="66.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="106.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="106.6640625" customWidth="1"/>
+    <col min="6" max="6" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="24" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -2369,7 +2393,7 @@
       <c r="G2" s="6">
         <v>10</v>
       </c>
-      <c r="H2" s="30">
+      <c r="H2" s="27">
         <v>3.61</v>
       </c>
       <c r="I2" s="7">
@@ -2377,7 +2401,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
@@ -2399,7 +2423,7 @@
       <c r="G3" s="6">
         <v>2</v>
       </c>
-      <c r="H3" s="30">
+      <c r="H3" s="27">
         <v>20.09</v>
       </c>
       <c r="I3" s="7">
@@ -2407,7 +2431,7 @@
         <v>40.18</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>18</v>
       </c>
@@ -2423,13 +2447,13 @@
         <v>1</v>
       </c>
       <c r="G4" s="5"/>
-      <c r="H4" s="30"/>
+      <c r="H4" s="27"/>
       <c r="I4" s="7">
         <f>Suggested!$H4*Suggested!$G4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>21</v>
       </c>
@@ -2451,7 +2475,7 @@
       <c r="G5" s="6">
         <v>10</v>
       </c>
-      <c r="H5" s="30">
+      <c r="H5" s="27">
         <v>0.25</v>
       </c>
       <c r="I5" s="7">
@@ -2459,7 +2483,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>25</v>
       </c>
@@ -2481,7 +2505,7 @@
       <c r="G6" s="6">
         <v>3</v>
       </c>
-      <c r="H6" s="30">
+      <c r="H6" s="27">
         <v>2.23</v>
       </c>
       <c r="I6" s="7">
@@ -2489,7 +2513,7 @@
         <v>6.6899999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>29</v>
       </c>
@@ -2511,7 +2535,7 @@
       <c r="G7" s="6">
         <v>3</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="27">
         <v>1.29</v>
       </c>
       <c r="I7" s="7">
@@ -2519,7 +2543,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>33</v>
       </c>
@@ -2541,7 +2565,7 @@
       <c r="G8" s="6">
         <v>2</v>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="27">
         <v>4.55</v>
       </c>
       <c r="I8" s="7">
@@ -2549,7 +2573,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>37</v>
       </c>
@@ -2571,7 +2595,7 @@
       <c r="G9" s="6">
         <v>2</v>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="27">
         <v>0.72</v>
       </c>
       <c r="I9" s="7">
@@ -2579,7 +2603,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>41</v>
       </c>
@@ -2601,7 +2625,7 @@
       <c r="G10" s="6">
         <v>5</v>
       </c>
-      <c r="H10" s="30">
+      <c r="H10" s="27">
         <v>1.94</v>
       </c>
       <c r="I10" s="7">
@@ -2609,7 +2633,7 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>45</v>
       </c>
@@ -2631,7 +2655,7 @@
       <c r="G11" s="6">
         <v>2</v>
       </c>
-      <c r="H11" s="30">
+      <c r="H11" s="27">
         <v>2.44</v>
       </c>
       <c r="I11" s="7">
@@ -2639,7 +2663,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>49</v>
       </c>
@@ -2661,7 +2685,7 @@
       <c r="G12" s="6">
         <v>1</v>
       </c>
-      <c r="H12" s="30">
+      <c r="H12" s="27">
         <v>42.9</v>
       </c>
       <c r="I12" s="7">
@@ -2669,7 +2693,7 @@
         <v>42.9</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>54</v>
       </c>
@@ -2691,7 +2715,7 @@
       <c r="G13" s="6">
         <v>1</v>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="27">
         <v>100.01</v>
       </c>
       <c r="I13" s="7">
@@ -2699,7 +2723,7 @@
         <v>100.01</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>58</v>
       </c>
@@ -2715,7 +2739,7 @@
       <c r="G14" s="5">
         <v>1</v>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="27">
         <v>70</v>
       </c>
       <c r="I14" s="7">
@@ -2723,7 +2747,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>60</v>
       </c>
@@ -2739,7 +2763,7 @@
       <c r="G15" s="5">
         <v>1</v>
       </c>
-      <c r="H15" s="30">
+      <c r="H15" s="27">
         <v>5</v>
       </c>
       <c r="I15" s="7">
@@ -2747,7 +2771,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>62</v>
       </c>
@@ -2763,15 +2787,15 @@
       <c r="G16" s="10">
         <v>1</v>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="15">
         <v>40</v>
       </c>
       <c r="I16" s="11">
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="23" t="s">
         <v>64</v>
       </c>
       <c r="B17" s="13" t="s">
@@ -2783,39 +2807,39 @@
       <c r="F17" s="12"/>
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
-      <c r="I17" s="25" cm="1">
+      <c r="I17" s="22" cm="1">
         <f t="array" ref="I17">SUM(I2:I16*0.2)</f>
         <v>74.474000000000004</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="22">
+      <c r="B18" s="20"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="19">
         <f>SUM($I$2:$I$17)</f>
         <v>446.84399999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+    <row r="19" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="19">
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="16">
         <f>SUM(I2:I13,I15:I16)+(0.2*SUM(I15:I16,I2:I13))</f>
         <v>362.84399999999999</v>
       </c>
